--- a/design/SE2026-G22-校园互助平台-人力成本折算(杭州2025社平工资).xlsx
+++ b/design/SE2026-G22-校园互助平台-人力成本折算(杭州2025社平工资).xlsx
@@ -73,7 +73,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -95,11 +95,55 @@
         <color rgb="00C7D2FE"/>
       </bottom>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00C7D2FE"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00C7D2FE"/>
+      </right>
+      <top style="thin">
+        <color rgb="00C7D2FE"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00C7D2FE"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00C7D2FE"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00C7D2FE"/>
+      </right>
+      <top style="thin">
+        <color rgb="00C7D2FE"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00C7D2FE"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -122,6 +166,8 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -196,6 +242,36 @@
     </indexedColors>
   </colors>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>7</col>
+      <colOff>0</colOff>
+      <row>0</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="742950" cy="742950"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -505,6 +581,12 @@
           <t>杭州 2025 年社会平均工资及小时 / 加班工资测算</t>
         </is>
       </c>
+      <c r="B1" s="8" t="n"/>
+      <c r="C1" s="8" t="n"/>
+      <c r="D1" s="8" t="n"/>
+      <c r="E1" s="8" t="n"/>
+      <c r="F1" s="8" t="n"/>
+      <c r="G1" s="9" t="n"/>
     </row>
     <row r="2" ht="34" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
@@ -659,6 +741,12 @@
           <t>SE2026-G22 校园互助平台项目 · 人力成本折算（项目总工作量 496.00 人时）</t>
         </is>
       </c>
+      <c r="B12" s="8" t="n"/>
+      <c r="C12" s="8" t="n"/>
+      <c r="D12" s="8" t="n"/>
+      <c r="E12" s="8" t="n"/>
+      <c r="F12" s="8" t="n"/>
+      <c r="G12" s="9" t="n"/>
     </row>
     <row r="13" ht="34" customHeight="1">
       <c r="A13" s="2" t="inlineStr">
@@ -791,5 +879,6 @@
     <mergeCell ref="A10:G10"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>